--- a/artfynd/A 65146-2021 artfynd.xlsx
+++ b/artfynd/A 65146-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127998812</v>
       </c>
       <c r="B2" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65146-2021 artfynd.xlsx
+++ b/artfynd/A 65146-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127998812</v>
       </c>
       <c r="B2" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65146-2021 artfynd.xlsx
+++ b/artfynd/A 65146-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127998812</v>
       </c>
       <c r="B2" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65146-2021 artfynd.xlsx
+++ b/artfynd/A 65146-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127998812</v>
       </c>
       <c r="B2" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65146-2021 artfynd.xlsx
+++ b/artfynd/A 65146-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127998812</v>
       </c>
       <c r="B2" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65146-2021 artfynd.xlsx
+++ b/artfynd/A 65146-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127998812</v>
       </c>
       <c r="B2" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65146-2021 artfynd.xlsx
+++ b/artfynd/A 65146-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127998812</v>
       </c>
       <c r="B2" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65146-2021 artfynd.xlsx
+++ b/artfynd/A 65146-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127998812</v>
       </c>
       <c r="B2" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65146-2021 artfynd.xlsx
+++ b/artfynd/A 65146-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127998812</v>
+        <v>119506833</v>
       </c>
       <c r="B2" t="n">
-        <v>91482</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541261</v>
+        <v>541476</v>
       </c>
       <c r="R2" t="n">
-        <v>7247056</v>
+        <v>7247092</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +773,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Granlåga grov, knäckt och på stubbe</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga grov, knäckt och på stubbe</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,6 +793,841 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127998769</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92208</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>658</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>541190</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7246938</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>4 st äldre fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granlåga rotknäckt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga rotknäckt</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127998806</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>541220</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7247067</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granlåga, mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119506848</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>541498</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7247159</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119506778</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>541526</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7247213</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119506801</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>541465</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7247101</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stöttes</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119506860</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>541527</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7247215</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119506862</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>541476</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7247094</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 22 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
